--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -626,7 +626,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -696,7 +696,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -766,7 +766,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -836,7 +836,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -906,7 +906,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -976,7 +976,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2166,7 +2166,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3566,7 +3566,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3846,7 +3846,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4056,7 +4056,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4686,7 +4686,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5386,7 +5386,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5876,7 +5876,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -5946,7 +5946,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6786,7 +6786,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6856,7 +6856,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7346,7 +7346,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7906,7 +7906,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8186,7 +8186,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8746,7 +8746,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -8956,7 +8956,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9026,7 +9026,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9166,7 +9166,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9236,7 +9236,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9306,7 +9306,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9656,7 +9656,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9796,7 +9796,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10146,7 +10146,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10216,7 +10216,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10286,7 +10286,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10356,7 +10356,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10496,7 +10496,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10776,7 +10776,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -10986,7 +10986,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11546,7 +11546,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11826,7 +11826,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -11966,7 +11966,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12036,7 +12036,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12106,7 +12106,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12176,7 +12176,7 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12246,7 +12246,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12386,7 +12386,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12526,7 +12526,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12666,7 +12666,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12736,7 +12736,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12876,7 +12876,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13016,7 +13016,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13156,7 +13156,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13226,7 +13226,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13296,7 +13296,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13436,7 +13436,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13576,7 +13576,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13786,7 +13786,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14066,7 +14066,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14136,7 +14136,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14206,7 +14206,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14276,7 +14276,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14416,7 +14416,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14556,7 +14556,7 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14696,7 +14696,7 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14766,7 +14766,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14836,7 +14836,7 @@
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15116,7 +15116,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15186,7 +15186,7 @@
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15256,7 +15256,7 @@
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15326,7 +15326,7 @@
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15396,7 +15396,7 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15536,7 +15536,7 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15676,7 +15676,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15816,7 +15816,7 @@
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15886,7 +15886,7 @@
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -15956,7 +15956,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16026,7 +16026,7 @@
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16096,7 +16096,7 @@
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16306,7 +16306,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16376,7 +16376,7 @@
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16446,7 +16446,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16516,7 +16516,7 @@
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16656,7 +16656,7 @@
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16726,7 +16726,7 @@
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16796,7 +16796,7 @@
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17006,7 +17006,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17146,7 +17146,7 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17286,7 +17286,7 @@
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17356,7 +17356,7 @@
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17426,7 +17426,7 @@
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17566,7 +17566,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17776,7 +17776,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -17986,7 +17986,7 @@
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18056,7 +18056,7 @@
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18126,7 +18126,7 @@
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18266,7 +18266,7 @@
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18406,7 +18406,7 @@
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18476,7 +18476,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18546,7 +18546,7 @@
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18616,7 +18616,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19036,7 +19036,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19106,7 +19106,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19246,7 +19246,7 @@
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19316,7 +19316,7 @@
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19386,7 +19386,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19456,7 +19456,7 @@
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19596,7 +19596,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19806,7 +19806,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19876,7 +19876,7 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20016,7 +20016,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20156,7 +20156,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20296,7 +20296,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20366,7 +20366,7 @@
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20436,7 +20436,7 @@
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20506,7 +20506,7 @@
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20576,7 +20576,7 @@
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20716,7 +20716,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20786,7 +20786,7 @@
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20856,7 +20856,7 @@
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Auth
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20926,7 +20926,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Patient-Dashboard
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -20996,7 +20996,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Doctor-Portal
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21066,7 +21066,7 @@
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to ASHA-Worker
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21136,7 +21136,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Pharmacy
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Admin-Security
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to UI-Theme
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21346,7 +21346,7 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Navigation
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21416,7 +21416,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Profile
 3. Perform workflow actions
 4. Verify UI state</t>
@@ -21486,7 +21486,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>1. Open Telemedicine SPA
+          <t>1. Open Olfactory Fossa Depth Portal
 2. Navigate to Notifications
 3. Perform workflow actions
 4. Verify UI state</t>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -574,12 +574,12 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:46</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:48</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 03:59:53</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -784,12 +784,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:02</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -854,12 +854,12 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -924,12 +924,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:13</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:19</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1134,12 +1134,12 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:06</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:21</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:09</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:15</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:39</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1554,12 +1554,12 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:26</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1624,12 +1624,12 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:55</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:29</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:59</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1834,12 +1834,12 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:36</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:15</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:22</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2044,12 +2044,12 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:45</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:52</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:53</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2254,12 +2254,12 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:01</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:50</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:00:46</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:40</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:43</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:44</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:13</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:48</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:21</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2884,12 +2884,12 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:19</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:39</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:05</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:44</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:15</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3234,12 +3234,12 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:57</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:27</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:27</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3444,12 +3444,12 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:22</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:15</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3584,12 +3584,12 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:07</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:09</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:04</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:01:41</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:41</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3934,12 +3934,12 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:05</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4004,12 +4004,12 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:53</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4074,12 +4074,12 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:55</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:23</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:28</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:58</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:41</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:37</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:51</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:30</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:06</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4704,12 +4704,12 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:49</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:46</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:44</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4914,12 +4914,12 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:19</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:03</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5054,12 +5054,12 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:11</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5124,12 +5124,12 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:52</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:11</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5264,12 +5264,12 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:03</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:58</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5404,12 +5404,12 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:36</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:07</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:11</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:44</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5684,12 +5684,12 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:37</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:39</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:02</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:12</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5964,12 +5964,12 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:02</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:26</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:45</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:55</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6244,12 +6244,12 @@
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:22</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:24</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:05</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:17</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:59</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:35</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:02</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:02:45</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:24</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:40</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:51</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:31</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:23</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:40</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:39</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:24</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7434,12 +7434,12 @@
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:00</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:32</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:16</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:53</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:21</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7784,12 +7784,12 @@
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:53</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:12</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -7924,12 +7924,12 @@
       </c>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:40</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7994,12 +7994,12 @@
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:42</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:49</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8204,12 +8204,12 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:47</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:35</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -8344,12 +8344,12 @@
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:38</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:00</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:29</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:09</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:59</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -8694,12 +8694,12 @@
       </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:21</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:02</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:32</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="J121" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:03:44</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:49</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9044,12 +9044,12 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:01</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9114,12 +9114,12 @@
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:56</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:30</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:29</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:59</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:09</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:22</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:43</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:29</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:54</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:48</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:28</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:12</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10024,12 +10024,12 @@
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:43</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:21</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:46</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:45</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:01</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10444,12 +10444,12 @@
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:51</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10514,12 +10514,12 @@
       </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:12</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:38</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -10654,12 +10654,12 @@
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:15</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="J147" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:27</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="J148" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:29</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -10864,12 +10864,12 @@
       </c>
       <c r="J149" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:59</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -10934,12 +10934,12 @@
       </c>
       <c r="J150" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:48</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="J151" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:16</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -11074,12 +11074,12 @@
       </c>
       <c r="J152" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:56</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
@@ -11144,12 +11144,12 @@
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:20</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -11214,12 +11214,12 @@
       </c>
       <c r="J154" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:04:52</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -11284,12 +11284,12 @@
       </c>
       <c r="J155" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:24</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
@@ -11354,12 +11354,12 @@
       </c>
       <c r="J156" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:35</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11424,12 +11424,12 @@
       </c>
       <c r="J157" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:17</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="J158" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:13</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
@@ -11564,12 +11564,12 @@
       </c>
       <c r="J159" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:16</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -11634,12 +11634,12 @@
       </c>
       <c r="J160" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:45</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -11704,12 +11704,12 @@
       </c>
       <c r="J161" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:24</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -11774,12 +11774,12 @@
       </c>
       <c r="J162" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:12</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="J163" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:05:33</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="J164" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:33</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -11984,12 +11984,12 @@
       </c>
       <c r="J165" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:51</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="J166" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:22</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:10</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12194,12 +12194,12 @@
       </c>
       <c r="J168" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:29</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12264,12 +12264,12 @@
       </c>
       <c r="J169" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:39</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12334,12 +12334,12 @@
       </c>
       <c r="J170" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:48</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12404,12 +12404,12 @@
       </c>
       <c r="J171" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:27</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12474,12 +12474,12 @@
       </c>
       <c r="J172" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:31</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
@@ -12544,12 +12544,12 @@
       </c>
       <c r="J173" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:11</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="J174" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:22</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="J175" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:41</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="J176" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:10</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -12824,12 +12824,12 @@
       </c>
       <c r="J177" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:40</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
@@ -12894,12 +12894,12 @@
       </c>
       <c r="J178" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:06</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="J179" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:45</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13034,12 +13034,12 @@
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:42</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13104,12 +13104,12 @@
       </c>
       <c r="J181" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:45</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="J182" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:02</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="J183" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:01</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="J184" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:59</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
@@ -13384,12 +13384,12 @@
       </c>
       <c r="J185" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:40</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13454,12 +13454,12 @@
       </c>
       <c r="J186" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:31</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
@@ -13524,12 +13524,12 @@
       </c>
       <c r="J187" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:39</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="J188" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:06</t>
         </is>
       </c>
       <c r="L188" t="inlineStr">
@@ -13664,12 +13664,12 @@
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:22</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="J190" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:58</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -13804,12 +13804,12 @@
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:55</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -13874,12 +13874,12 @@
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:42</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -13944,12 +13944,12 @@
       </c>
       <c r="J193" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:06:34</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:36</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -14084,12 +14084,12 @@
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:45</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14154,12 +14154,12 @@
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:05</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:31</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:27</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14364,12 +14364,12 @@
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:59</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:20</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -14504,12 +14504,12 @@
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:18</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -14574,12 +14574,12 @@
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:43</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:15</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
@@ -14714,12 +14714,12 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:44</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="J206" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:56</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="J207" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:48</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -14994,12 +14994,12 @@
       </c>
       <c r="J208" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:28</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="J209" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:22</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
@@ -15134,12 +15134,12 @@
       </c>
       <c r="J210" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:08</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
@@ -15204,12 +15204,12 @@
       </c>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:25</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15274,12 +15274,12 @@
       </c>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:07</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15344,12 +15344,12 @@
       </c>
       <c r="J213" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:46</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15414,12 +15414,12 @@
       </c>
       <c r="J214" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:40</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -15484,12 +15484,12 @@
       </c>
       <c r="J215" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:06</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="J216" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:05</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -15624,12 +15624,12 @@
       </c>
       <c r="J217" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:31</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -15694,12 +15694,12 @@
       </c>
       <c r="J218" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:38</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -15764,12 +15764,12 @@
       </c>
       <c r="J219" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:04</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -15834,12 +15834,12 @@
       </c>
       <c r="J220" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:14</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -15904,12 +15904,12 @@
       </c>
       <c r="J221" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:47</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -15974,12 +15974,12 @@
       </c>
       <c r="J222" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:49</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -16044,12 +16044,12 @@
       </c>
       <c r="J223" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:07:16</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="J224" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:26</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -16184,12 +16184,12 @@
       </c>
       <c r="J225" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:08</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16254,12 +16254,12 @@
       </c>
       <c r="J226" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:07</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
@@ -16324,12 +16324,12 @@
       </c>
       <c r="J227" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:03</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
@@ -16394,12 +16394,12 @@
       </c>
       <c r="J228" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:54</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
@@ -16464,12 +16464,12 @@
       </c>
       <c r="J229" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:08</t>
         </is>
       </c>
       <c r="L229" t="inlineStr">
@@ -16534,12 +16534,12 @@
       </c>
       <c r="J230" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:58</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
@@ -16604,12 +16604,12 @@
       </c>
       <c r="J231" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:29</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
@@ -16674,12 +16674,12 @@
       </c>
       <c r="J232" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:31</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -16744,12 +16744,12 @@
       </c>
       <c r="J233" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:13</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -16814,12 +16814,12 @@
       </c>
       <c r="J234" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:01</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -16884,12 +16884,12 @@
       </c>
       <c r="J235" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:34</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
@@ -16954,12 +16954,12 @@
       </c>
       <c r="J236" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:35</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
@@ -17024,12 +17024,12 @@
       </c>
       <c r="J237" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:00</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="J238" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:02</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
@@ -17164,12 +17164,12 @@
       </c>
       <c r="J239" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:39</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
@@ -17234,12 +17234,12 @@
       </c>
       <c r="J240" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:20</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
@@ -17304,12 +17304,12 @@
       </c>
       <c r="J241" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:45</t>
         </is>
       </c>
       <c r="L241" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="J242" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:47</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -17444,12 +17444,12 @@
       </c>
       <c r="J243" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:04</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -17514,12 +17514,12 @@
       </c>
       <c r="J244" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:45</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="J245" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:14</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
@@ -17654,12 +17654,12 @@
       </c>
       <c r="J246" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:45</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -17724,12 +17724,12 @@
       </c>
       <c r="J247" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -17794,12 +17794,12 @@
       </c>
       <c r="J248" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:53</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -17864,12 +17864,12 @@
       </c>
       <c r="J249" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:40</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="J250" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:32</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -18004,12 +18004,12 @@
       </c>
       <c r="J251" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:57</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="J252" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:18</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -18144,12 +18144,12 @@
       </c>
       <c r="J253" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:49</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -18214,12 +18214,12 @@
       </c>
       <c r="J254" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:27</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="J255" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:08:57</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -18354,12 +18354,12 @@
       </c>
       <c r="J256" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:27</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -18424,12 +18424,12 @@
       </c>
       <c r="J257" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:33</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -18494,12 +18494,12 @@
       </c>
       <c r="J258" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:57</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
@@ -18564,12 +18564,12 @@
       </c>
       <c r="J259" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:52</t>
         </is>
       </c>
       <c r="L259" t="inlineStr">
@@ -18634,12 +18634,12 @@
       </c>
       <c r="J260" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:03</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -18704,12 +18704,12 @@
       </c>
       <c r="J261" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:55</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -18774,12 +18774,12 @@
       </c>
       <c r="J262" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:27</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -18844,12 +18844,12 @@
       </c>
       <c r="J263" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:25</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -18914,12 +18914,12 @@
       </c>
       <c r="J264" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:17</t>
         </is>
       </c>
       <c r="L264" t="inlineStr">
@@ -18984,12 +18984,12 @@
       </c>
       <c r="J265" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:19</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19054,12 +19054,12 @@
       </c>
       <c r="J266" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:21</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -19124,12 +19124,12 @@
       </c>
       <c r="J267" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:03</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -19194,12 +19194,12 @@
       </c>
       <c r="J268" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:55</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -19264,12 +19264,12 @@
       </c>
       <c r="J269" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:19</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -19334,12 +19334,12 @@
       </c>
       <c r="J270" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:04</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -19404,12 +19404,12 @@
       </c>
       <c r="J271" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:00</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -19474,12 +19474,12 @@
       </c>
       <c r="J272" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:10</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -19544,12 +19544,12 @@
       </c>
       <c r="J273" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:03</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -19614,12 +19614,12 @@
       </c>
       <c r="J274" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:57</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -19684,12 +19684,12 @@
       </c>
       <c r="J275" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:59</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">
@@ -19754,12 +19754,12 @@
       </c>
       <c r="J276" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:09</t>
         </is>
       </c>
       <c r="L276" t="inlineStr">
@@ -19824,12 +19824,12 @@
       </c>
       <c r="J277" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:40</t>
         </is>
       </c>
       <c r="L277" t="inlineStr">
@@ -19894,12 +19894,12 @@
       </c>
       <c r="J278" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:23</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
@@ -19964,12 +19964,12 @@
       </c>
       <c r="J279" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:13:18</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
@@ -20034,12 +20034,12 @@
       </c>
       <c r="J280" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:15:50</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
@@ -20104,12 +20104,12 @@
       </c>
       <c r="J281" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:32</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
@@ -20174,12 +20174,12 @@
       </c>
       <c r="J282" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:21:24</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
@@ -20244,12 +20244,12 @@
       </c>
       <c r="J283" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:20:31</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
@@ -20314,12 +20314,12 @@
       </c>
       <c r="J284" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:56</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -20384,12 +20384,12 @@
       </c>
       <c r="J285" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:05</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -20454,12 +20454,12 @@
       </c>
       <c r="J286" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:06</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
@@ -20524,12 +20524,12 @@
       </c>
       <c r="J287" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:19:51</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
@@ -20594,12 +20594,12 @@
       </c>
       <c r="J288" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:34</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
@@ -20664,12 +20664,12 @@
       </c>
       <c r="J289" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:22:06</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
@@ -20734,12 +20734,12 @@
       </c>
       <c r="J290" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:18:11</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
@@ -20804,12 +20804,12 @@
       </c>
       <c r="J291" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:11:44</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
@@ -20874,12 +20874,12 @@
       </c>
       <c r="J292" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:23:47</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
@@ -20944,12 +20944,12 @@
       </c>
       <c r="J293" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:17:11</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
@@ -21014,12 +21014,12 @@
       </c>
       <c r="J294" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:59</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -21084,12 +21084,12 @@
       </c>
       <c r="J295" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:20</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="J296" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:10:53</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -21224,12 +21224,12 @@
       </c>
       <c r="J297" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:16:51</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -21294,12 +21294,12 @@
       </c>
       <c r="J298" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:14:45</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -21364,12 +21364,12 @@
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:24:11</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -21434,12 +21434,12 @@
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:09:54</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -21504,12 +21504,12 @@
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>2026-07-24 15:34:48</t>
+          <t>2026-07-25 04:12:47</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,14 +32,8 @@
     <font>
       <color rgb="00006100"/>
     </font>
-    <font>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <color rgb="009C6500"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -58,18 +52,6 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-        <bgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -83,18 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -603,7 +579,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>353ms</t>
+          <t>816ms</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -669,7 +645,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>602ms</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -735,7 +711,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>819ms</t>
+          <t>664ms</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -801,7 +777,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>433ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -867,7 +843,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>294ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -933,7 +909,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>481ms</t>
+          <t>677ms</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -998,7 +974,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>588ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1064,7 +1040,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>412ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1130,7 +1106,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>503ms</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1196,7 +1172,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>607ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1262,7 +1238,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>793ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1327,7 +1303,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1393,7 +1369,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>355ms</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1459,7 +1435,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>718ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1525,7 +1501,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>187ms</t>
+          <t>674ms</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1591,7 +1567,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>776ms</t>
+          <t>721ms</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1656,7 +1632,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>272ms</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1722,7 +1698,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>339ms</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1788,7 +1764,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>575ms</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1854,7 +1830,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>264ms</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1920,7 +1896,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>804ms</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1986,7 +1962,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>267ms</t>
+          <t>811ms</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2051,7 +2027,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>517ms</t>
+          <t>250ms</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2117,7 +2093,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>124ms</t>
+          <t>789ms</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2183,7 +2159,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>796ms</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2249,7 +2225,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2316,7 +2292,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>403ms</t>
+          <t>381ms</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2383,7 +2359,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>410ms</t>
+          <t>685ms</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2449,7 +2425,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>332ms</t>
+          <t>676ms</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2515,7 +2491,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>717ms</t>
+          <t>344ms</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2581,7 +2557,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>328ms</t>
+          <t>810ms</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2647,7 +2623,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>264ms</t>
+          <t>456ms</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2712,7 +2688,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>462ms</t>
+          <t>158ms</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2778,7 +2754,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>372ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2842,7 +2818,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>743ms</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2906,7 +2882,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>328ms</t>
+          <t>762ms</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2970,7 +2946,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>666ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3035,7 +3011,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>482ms</t>
+          <t>135ms</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3100,7 +3076,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>534ms</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3166,7 +3142,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>239ms</t>
+          <t>447ms</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3232,7 +3208,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>151ms</t>
+          <t>449ms</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3298,7 +3274,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>761ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3354,27 +3330,23 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Fail. Bug: Sign-up validation alert did not render in Edge.</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass. UI updated and database verification succeeded.</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2616ms</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>screenshots/fail_web_043.png</t>
-        </is>
-      </c>
+          <t>285ms</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Bug: Sign-up validation alert did not render in Edge.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3406,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>460ms</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3500,7 +3472,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3565,7 +3537,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3631,7 +3603,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>450ms</t>
+          <t>439ms</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3697,7 +3669,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>748ms</t>
+          <t>813ms</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3763,7 +3735,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>513ms</t>
+          <t>649ms</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3829,7 +3801,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>638ms</t>
+          <t>308ms</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3894,7 +3866,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>268ms</t>
+          <t>679ms</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3960,7 +3932,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>407ms</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -4026,7 +3998,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>419ms</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4092,7 +4064,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4158,7 +4130,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>364ms</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4223,7 +4195,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>780ms</t>
+          <t>371ms</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4289,7 +4261,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -4355,7 +4327,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>175ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4421,7 +4393,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>136ms</t>
+          <t>681ms</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4487,7 +4459,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>726ms</t>
+          <t>183ms</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -4553,7 +4525,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>526ms</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -4618,7 +4590,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>652ms</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4684,7 +4656,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>318ms</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4750,7 +4722,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>661ms</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4816,7 +4788,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>663ms</t>
+          <t>202ms</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4883,7 +4855,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>656ms</t>
+          <t>171ms</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4950,7 +4922,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>274ms</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -5016,7 +4988,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>589ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5082,7 +5054,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>126ms</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5148,7 +5120,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>664ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5214,7 +5186,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>325ms</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5279,7 +5251,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>184ms</t>
+          <t>676ms</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5345,7 +5317,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>834ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5409,7 +5381,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5473,7 +5445,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>612ms</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5537,7 +5509,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>443ms</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5602,7 +5574,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>624ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -5667,7 +5639,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>356ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -5733,7 +5705,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>258ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5799,7 +5771,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>564ms</t>
+          <t>271ms</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5865,7 +5837,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>147ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5931,7 +5903,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>668ms</t>
+          <t>829ms</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5997,7 +5969,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>492ms</t>
+          <t>838ms</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6063,7 +6035,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>261ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6128,7 +6100,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>198ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6194,7 +6166,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>582ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6260,7 +6232,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>141ms</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6326,7 +6298,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>519ms</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6392,7 +6364,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>533ms</t>
+          <t>803ms</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6457,7 +6429,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>659ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6523,7 +6495,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>713ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6589,7 +6561,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>240ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6655,7 +6627,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>133ms</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -6721,7 +6693,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6786,7 +6758,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>558ms</t>
+          <t>136ms</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -6852,7 +6824,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>429ms</t>
+          <t>533ms</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6918,7 +6890,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>622ms</t>
+          <t>454ms</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6984,7 +6956,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -7050,7 +7022,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>156ms</t>
+          <t>509ms</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7116,7 +7088,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>791ms</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7181,7 +7153,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>727ms</t>
+          <t>647ms</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -7247,7 +7219,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>259ms</t>
+          <t>425ms</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7313,7 +7285,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>197ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -7379,7 +7351,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>466ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7446,7 +7418,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>756ms</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -7513,7 +7485,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>733ms</t>
+          <t>608ms</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -7579,7 +7551,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>705ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -7645,7 +7617,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>414ms</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -7711,7 +7683,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>677ms</t>
+          <t>471ms</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -7777,7 +7749,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>688ms</t>
+          <t>271ms</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -7842,7 +7814,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>247ms</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -7908,7 +7880,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>620ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -7972,7 +7944,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>192ms</t>
+          <t>440ms</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -8036,7 +8008,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -8090,27 +8062,23 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Fail. Bug: Sign-up validation alert did not render in Edge.</t>
-        </is>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>Fail</t>
+          <t>Pass. UI updated and database verification succeeded.</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>3504ms</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>screenshots/fail_web_115.png</t>
-        </is>
-      </c>
+          <t>334ms</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Bug: Sign-up validation alert did not render in Edge.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8137,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>673ms</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -8234,7 +8202,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>145ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -8300,7 +8268,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>216ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -8366,7 +8334,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>134ms</t>
+          <t>510ms</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -8432,7 +8400,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -8498,7 +8466,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>760ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -8564,7 +8532,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>494ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -8630,7 +8598,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>425ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -8695,7 +8663,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>772ms</t>
+          <t>266ms</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -8761,7 +8729,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>764ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -8827,7 +8795,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>120ms</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -8893,7 +8861,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>675ms</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -8959,7 +8927,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>811ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -9024,7 +8992,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>817ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -9090,7 +9058,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>485ms</t>
+          <t>394ms</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -9156,7 +9124,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -9222,7 +9190,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>826ms</t>
+          <t>570ms</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -9288,7 +9256,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>199ms</t>
+          <t>345ms</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -9353,7 +9321,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>466ms</t>
+          <t>261ms</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -9419,7 +9387,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -9485,7 +9453,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>467ms</t>
+          <t>551ms</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -9551,7 +9519,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>694ms</t>
+          <t>129ms</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -9617,7 +9585,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>370ms</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -9683,7 +9651,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>291ms</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -9748,7 +9716,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -9814,7 +9782,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>539ms</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -9880,7 +9848,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>605ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -9946,7 +9914,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -10013,7 +9981,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>583ms</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -10080,7 +10048,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>346ms</t>
+          <t>181ms</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -10146,7 +10114,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>612ms</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -10212,7 +10180,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>373ms</t>
+          <t>773ms</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -10278,7 +10246,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>755ms</t>
+          <t>446ms</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -10344,7 +10312,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>807ms</t>
+          <t>651ms</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -10409,7 +10377,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>816ms</t>
+          <t>603ms</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -10475,7 +10443,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>562ms</t>
+          <t>321ms</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -10539,7 +10507,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>377ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -10603,7 +10571,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>316ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -10667,7 +10635,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>642ms</t>
+          <t>183ms</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -10732,7 +10700,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>417ms</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -10797,7 +10765,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>363ms</t>
+          <t>316ms</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -10863,7 +10831,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>486ms</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -10929,7 +10897,7 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>536ms</t>
+          <t>424ms</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
@@ -10995,7 +10963,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>256ms</t>
+          <t>364ms</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -11061,7 +11029,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>320ms</t>
+          <t>839ms</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
@@ -11127,7 +11095,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>815ms</t>
+          <t>761ms</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -11193,7 +11161,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>546ms</t>
+          <t>170ms</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -11258,7 +11226,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>401ms</t>
+          <t>247ms</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -11324,7 +11292,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>521ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -11390,7 +11358,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>231ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -11456,7 +11424,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>529ms</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -11522,7 +11490,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -11587,7 +11555,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -11653,7 +11621,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>197ms</t>
+          <t>191ms</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -11719,7 +11687,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>333ms</t>
+          <t>469ms</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -11785,7 +11753,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>311ms</t>
+          <t>351ms</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -11851,7 +11819,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>398ms</t>
+          <t>453ms</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -11916,7 +11884,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>155ms</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -11982,7 +11950,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -12048,7 +12016,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -12114,7 +12082,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>823ms</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -12180,7 +12148,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>518ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -12246,7 +12214,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>474ms</t>
+          <t>193ms</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -12311,7 +12279,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>751ms</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -12377,7 +12345,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>697ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -12443,7 +12411,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>747ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -12509,7 +12477,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>204ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
@@ -12576,7 +12544,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>613ms</t>
+          <t>621ms</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -12643,7 +12611,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>847ms</t>
+          <t>376ms</t>
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
@@ -12709,7 +12677,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>777ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -12775,7 +12743,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>473ms</t>
+          <t>671ms</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
@@ -12841,7 +12809,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>513ms</t>
+          <t>440ms</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
@@ -12907,7 +12875,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>614ms</t>
+          <t>630ms</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
@@ -12972,7 +12940,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
@@ -13038,7 +13006,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>281ms</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -13102,7 +13070,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
@@ -13166,7 +13134,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>739ms</t>
+          <t>434ms</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -13230,7 +13198,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>379ms</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
@@ -13295,7 +13263,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>296ms</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
@@ -13360,7 +13328,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>716ms</t>
+          <t>495ms</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
@@ -13426,7 +13394,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>684ms</t>
+          <t>457ms</t>
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
@@ -13492,7 +13460,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>786ms</t>
+          <t>477ms</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
@@ -13558,7 +13526,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>326ms</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -13624,7 +13592,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>783ms</t>
+          <t>456ms</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
@@ -13690,7 +13658,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -13746,23 +13714,23 @@
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Skip. Feature Skip: OAuth validation skipped because Google Auth integration is disabled.</t>
-        </is>
-      </c>
-      <c r="J202" s="4" t="inlineStr">
-        <is>
-          <t>Skip</t>
+          <t>Pass. UI updated and database verification succeeded.</t>
+        </is>
+      </c>
+      <c r="J202" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>0ms</t>
+          <t>512ms</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Feature Skip: OAuth validation skipped because Google Auth integration is disabled.</t>
+          <t>Verified successfully.</t>
         </is>
       </c>
     </row>
@@ -13821,7 +13789,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>378ms</t>
+          <t>527ms</t>
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
@@ -13887,7 +13855,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>561ms</t>
+          <t>223ms</t>
         </is>
       </c>
       <c r="L204" t="inlineStr"/>
@@ -13953,7 +13921,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>331ms</t>
+          <t>159ms</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
@@ -14019,7 +13987,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>235ms</t>
+          <t>280ms</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
@@ -14085,7 +14053,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>458ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -14150,7 +14118,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>823ms</t>
+          <t>209ms</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -14216,7 +14184,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>167ms</t>
+          <t>718ms</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
@@ -14282,7 +14250,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>223ms</t>
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
@@ -14348,7 +14316,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
@@ -14414,7 +14382,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>848ms</t>
+          <t>554ms</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
@@ -14479,7 +14447,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>479ms</t>
         </is>
       </c>
       <c r="L213" t="inlineStr"/>
@@ -14545,7 +14513,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>770ms</t>
+          <t>312ms</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
@@ -14611,7 +14579,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>174ms</t>
+          <t>468ms</t>
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
@@ -14677,7 +14645,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>185ms</t>
+          <t>161ms</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -14743,7 +14711,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>164ms</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -14809,7 +14777,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>445ms</t>
+          <t>218ms</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -14874,7 +14842,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>788ms</t>
+          <t>792ms</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -14940,7 +14908,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>389ms</t>
+          <t>580ms</t>
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
@@ -15006,7 +14974,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>329ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="L221" t="inlineStr"/>
@@ -15072,7 +15040,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>284ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -15139,7 +15107,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>650ms</t>
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
@@ -15206,7 +15174,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>775ms</t>
+          <t>584ms</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
@@ -15272,7 +15240,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>160ms</t>
+          <t>448ms</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -15338,7 +15306,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>849ms</t>
+          <t>769ms</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -15404,7 +15372,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>815ms</t>
+          <t>731ms</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -15470,7 +15438,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>421ms</t>
+          <t>515ms</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -15535,7 +15503,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>176ms</t>
+          <t>444ms</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -15601,7 +15569,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>541ms</t>
+          <t>698ms</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -15665,7 +15633,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
@@ -15729,7 +15697,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>245ms</t>
+          <t>286ms</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -15793,7 +15761,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>127ms</t>
+          <t>839ms</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -15858,7 +15826,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>547ms</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -15923,7 +15891,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>499ms</t>
+          <t>568ms</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -15989,7 +15957,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>312ms</t>
+          <t>733ms</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -16055,7 +16023,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>627ms</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -16121,7 +16089,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -16187,7 +16155,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>556ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -16253,7 +16221,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>435ms</t>
         </is>
       </c>
       <c r="L240" t="inlineStr"/>
@@ -16319,7 +16287,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>366ms</t>
         </is>
       </c>
       <c r="L241" t="inlineStr"/>
@@ -16384,7 +16352,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>297ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="L242" t="inlineStr"/>
@@ -16450,7 +16418,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>523ms</t>
+          <t>154ms</t>
         </is>
       </c>
       <c r="L243" t="inlineStr"/>
@@ -16516,7 +16484,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>805ms</t>
+          <t>725ms</t>
         </is>
       </c>
       <c r="L244" t="inlineStr"/>
@@ -16582,7 +16550,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>572ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="L245" t="inlineStr"/>
@@ -16648,7 +16616,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>193ms</t>
+          <t>230ms</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -16713,7 +16681,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>427ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -16779,7 +16747,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>590ms</t>
+          <t>493ms</t>
         </is>
       </c>
       <c r="L248" t="inlineStr"/>
@@ -16845,7 +16813,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>244ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="L249" t="inlineStr"/>
@@ -16911,7 +16879,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>637ms</t>
+          <t>327ms</t>
         </is>
       </c>
       <c r="L250" t="inlineStr"/>
@@ -16977,7 +16945,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="L251" t="inlineStr"/>
@@ -17042,7 +17010,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>342ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="L252" t="inlineStr"/>
@@ -17108,7 +17076,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>385ms</t>
+          <t>304ms</t>
         </is>
       </c>
       <c r="L253" t="inlineStr"/>
@@ -17174,7 +17142,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>475ms</t>
+          <t>586ms</t>
         </is>
       </c>
       <c r="L254" t="inlineStr"/>
@@ -17240,7 +17208,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>617ms</t>
+          <t>813ms</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -17306,7 +17274,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>542ms</t>
+          <t>399ms</t>
         </is>
       </c>
       <c r="L256" t="inlineStr"/>
@@ -17372,7 +17340,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>432ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -17437,7 +17405,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>609ms</t>
+          <t>600ms</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -17503,7 +17471,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>212ms</t>
+          <t>767ms</t>
         </is>
       </c>
       <c r="L259" t="inlineStr"/>
@@ -17569,7 +17537,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>678ms</t>
+          <t>596ms</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -17635,7 +17603,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>766ms</t>
         </is>
       </c>
       <c r="L261" t="inlineStr"/>
@@ -17702,7 +17670,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>470ms</t>
+          <t>568ms</t>
         </is>
       </c>
       <c r="L262" t="inlineStr"/>
@@ -17769,7 +17737,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="L263" t="inlineStr"/>
@@ -17835,7 +17803,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>545ms</t>
+          <t>707ms</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -17901,7 +17869,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>657ms</t>
+          <t>190ms</t>
         </is>
       </c>
       <c r="L265" t="inlineStr"/>
@@ -17967,7 +17935,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>700ms</t>
+          <t>667ms</t>
         </is>
       </c>
       <c r="L266" t="inlineStr"/>
@@ -18033,7 +18001,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="L267" t="inlineStr"/>
@@ -18098,7 +18066,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>130ms</t>
+          <t>428ms</t>
         </is>
       </c>
       <c r="L268" t="inlineStr"/>
@@ -18164,7 +18132,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -18228,7 +18196,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>221ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="L270" t="inlineStr"/>
@@ -18292,7 +18260,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>484ms</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -18356,7 +18324,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>758ms</t>
+          <t>599ms</t>
         </is>
       </c>
       <c r="L272" t="inlineStr"/>
@@ -18421,7 +18389,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>560ms</t>
+          <t>317ms</t>
         </is>
       </c>
       <c r="L273" t="inlineStr"/>
@@ -18486,7 +18454,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>689ms</t>
+          <t>144ms</t>
         </is>
       </c>
       <c r="L274" t="inlineStr"/>
@@ -18552,7 +18520,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>580ms</t>
+          <t>683ms</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -18618,7 +18586,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>490ms</t>
+          <t>330ms</t>
         </is>
       </c>
       <c r="L276" t="inlineStr"/>
@@ -18684,7 +18652,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>656ms</t>
         </is>
       </c>
       <c r="L277" t="inlineStr"/>
@@ -18750,7 +18718,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>746ms</t>
+          <t>644ms</t>
         </is>
       </c>
       <c r="L278" t="inlineStr"/>
@@ -18816,7 +18784,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>256ms</t>
+          <t>567ms</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -18882,7 +18850,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>563ms</t>
+          <t>398ms</t>
         </is>
       </c>
       <c r="L280" t="inlineStr"/>
@@ -18947,7 +18915,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>712ms</t>
+          <t>566ms</t>
         </is>
       </c>
       <c r="L281" t="inlineStr"/>
@@ -19013,7 +18981,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>578ms</t>
+          <t>201ms</t>
         </is>
       </c>
       <c r="L282" t="inlineStr"/>
@@ -19079,7 +19047,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>179ms</t>
+          <t>803ms</t>
         </is>
       </c>
       <c r="L283" t="inlineStr"/>
@@ -19145,7 +19113,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>420ms</t>
         </is>
       </c>
       <c r="L284" t="inlineStr"/>
@@ -19211,7 +19179,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>766ms</t>
+          <t>623ms</t>
         </is>
       </c>
       <c r="L285" t="inlineStr"/>
@@ -19276,7 +19244,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>609ms</t>
+          <t>613ms</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
@@ -19342,7 +19310,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>674ms</t>
+          <t>255ms</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -19408,7 +19376,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>618ms</t>
+          <t>636ms</t>
         </is>
       </c>
       <c r="L288" t="inlineStr"/>
@@ -19474,7 +19442,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>168ms</t>
         </is>
       </c>
       <c r="L289" t="inlineStr"/>
@@ -19540,7 +19508,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>658ms</t>
+          <t>461ms</t>
         </is>
       </c>
       <c r="L290" t="inlineStr"/>
@@ -19605,7 +19573,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>832ms</t>
+          <t>404ms</t>
         </is>
       </c>
       <c r="L291" t="inlineStr"/>
@@ -19671,7 +19639,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>207ms</t>
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
@@ -19737,7 +19705,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>413ms</t>
+          <t>510ms</t>
         </is>
       </c>
       <c r="L293" t="inlineStr"/>
@@ -19803,7 +19771,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>251ms</t>
+          <t>185ms</t>
         </is>
       </c>
       <c r="L294" t="inlineStr"/>
@@ -19869,7 +19837,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>292ms</t>
+          <t>512ms</t>
         </is>
       </c>
       <c r="L295" t="inlineStr"/>
@@ -19935,7 +19903,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>441ms</t>
+          <t>167ms</t>
         </is>
       </c>
       <c r="L296" t="inlineStr"/>
@@ -20000,7 +19968,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>809ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="L297" t="inlineStr"/>
@@ -20066,7 +20034,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>594ms</t>
+          <t>323ms</t>
         </is>
       </c>
       <c r="L298" t="inlineStr"/>
@@ -20132,7 +20100,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>390ms</t>
+          <t>544ms</t>
         </is>
       </c>
       <c r="L299" t="inlineStr"/>
@@ -20198,7 +20166,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>841ms</t>
         </is>
       </c>
       <c r="L300" t="inlineStr"/>
@@ -20265,7 +20233,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>537ms</t>
+          <t>174ms</t>
         </is>
       </c>
       <c r="L301" t="inlineStr"/>

--- a/reports/Automation_Test_Report.xlsx
+++ b/reports/Automation_Test_Report.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>816ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -645,7 +645,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>602ms</t>
+          <t>468ms</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
@@ -711,7 +711,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>664ms</t>
+          <t>503ms</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -777,7 +777,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>781ms</t>
+          <t>669ms</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -843,7 +843,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>380ms</t>
+          <t>411ms</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -909,7 +909,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>677ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>625ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>455ms</t>
+          <t>296ms</t>
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>503ms</t>
+          <t>749ms</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>132ms</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>604ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
@@ -1303,7 +1303,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>142ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>355ms</t>
+          <t>571ms</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>146ms</t>
+          <t>529ms</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>674ms</t>
+          <t>448ms</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>721ms</t>
+          <t>212ms</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>272ms</t>
+          <t>559ms</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>339ms</t>
+          <t>742ms</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>575ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>264ms</t>
+          <t>789ms</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>804ms</t>
+          <t>842ms</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>811ms</t>
+          <t>835ms</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>250ms</t>
+          <t>421ms</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>789ms</t>
+          <t>806ms</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>796ms</t>
+          <t>139ms</t>
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
@@ -2225,7 +2225,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>537ms</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>381ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>685ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>676ms</t>
+          <t>236ms</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>344ms</t>
+          <t>361ms</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>810ms</t>
+          <t>204ms</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>456ms</t>
+          <t>238ms</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>158ms</t>
+          <t>540ms</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>151ms</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>743ms</t>
+          <t>198ms</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>762ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
@@ -2946,7 +2946,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>234ms</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>135ms</t>
+          <t>619ms</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>534ms</t>
+          <t>377ms</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>447ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>449ms</t>
+          <t>343ms</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>774ms</t>
+          <t>546ms</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>285ms</t>
+          <t>467ms</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>460ms</t>
+          <t>498ms</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>222ms</t>
+          <t>465ms</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
@@ -3537,7 +3537,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>435ms</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>439ms</t>
+          <t>690ms</t>
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>813ms</t>
+          <t>741ms</t>
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>649ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>308ms</t>
+          <t>429ms</t>
         </is>
       </c>
       <c r="L51" t="inlineStr"/>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>679ms</t>
+          <t>781ms</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>407ms</t>
+          <t>294ms</t>
         </is>
       </c>
       <c r="L53" t="inlineStr"/>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>419ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
@@ -4064,7 +4064,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>601ms</t>
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>386ms</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>371ms</t>
+          <t>577ms</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>501ms</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>277ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>681ms</t>
+          <t>736ms</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>183ms</t>
+          <t>135ms</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>526ms</t>
+          <t>208ms</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -4590,7 +4590,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>652ms</t>
+          <t>199ms</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>318ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>661ms</t>
+          <t>793ms</t>
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>202ms</t>
+          <t>194ms</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>171ms</t>
+          <t>691ms</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>274ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="L68" t="inlineStr"/>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>415ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>126ms</t>
+          <t>663ms</t>
         </is>
       </c>
       <c r="L70" t="inlineStr"/>
@@ -5120,7 +5120,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>140ms</t>
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>325ms</t>
+          <t>705ms</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -5251,7 +5251,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>676ms</t>
+          <t>595ms</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -5317,7 +5317,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="L74" t="inlineStr"/>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>143ms</t>
         </is>
       </c>
       <c r="L75" t="inlineStr"/>
@@ -5445,7 +5445,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>612ms</t>
+          <t>452ms</t>
         </is>
       </c>
       <c r="L76" t="inlineStr"/>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>443ms</t>
+          <t>818ms</t>
         </is>
       </c>
       <c r="L77" t="inlineStr"/>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>199ms</t>
+          <t>197ms</t>
         </is>
       </c>
       <c r="L78" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>710ms</t>
         </is>
       </c>
       <c r="L79" t="inlineStr"/>
@@ -5705,7 +5705,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>741ms</t>
+          <t>178ms</t>
         </is>
       </c>
       <c r="L80" t="inlineStr"/>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>704ms</t>
         </is>
       </c>
       <c r="L81" t="inlineStr"/>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>825ms</t>
+          <t>672ms</t>
         </is>
       </c>
       <c r="L82" t="inlineStr"/>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>829ms</t>
+          <t>273ms</t>
         </is>
       </c>
       <c r="L83" t="inlineStr"/>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>838ms</t>
+          <t>184ms</t>
         </is>
       </c>
       <c r="L84" t="inlineStr"/>
@@ -6035,7 +6035,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>837ms</t>
+          <t>392ms</t>
         </is>
       </c>
       <c r="L85" t="inlineStr"/>
@@ -6100,7 +6100,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>794ms</t>
+          <t>414ms</t>
         </is>
       </c>
       <c r="L86" t="inlineStr"/>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>768ms</t>
         </is>
       </c>
       <c r="L87" t="inlineStr"/>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>141ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="L88" t="inlineStr"/>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>519ms</t>
+          <t>480ms</t>
         </is>
       </c>
       <c r="L89" t="inlineStr"/>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>803ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="L90" t="inlineStr"/>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="L91" t="inlineStr"/>
@@ -6495,7 +6495,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="L92" t="inlineStr"/>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>761ms</t>
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>133ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="L94" t="inlineStr"/>
@@ -6693,7 +6693,7 @@
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>299ms</t>
+          <t>147ms</t>
         </is>
       </c>
       <c r="L95" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>136ms</t>
+          <t>506ms</t>
         </is>
       </c>
       <c r="L96" t="inlineStr"/>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>533ms</t>
+          <t>759ms</t>
         </is>
       </c>
       <c r="L97" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>454ms</t>
+          <t>169ms</t>
         </is>
       </c>
       <c r="L98" t="inlineStr"/>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>607ms</t>
         </is>
       </c>
       <c r="L99" t="inlineStr"/>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>509ms</t>
+          <t>466ms</t>
         </is>
       </c>
       <c r="L100" t="inlineStr"/>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>791ms</t>
+          <t>639ms</t>
         </is>
       </c>
       <c r="L101" t="inlineStr"/>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>647ms</t>
+          <t>289ms</t>
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>425ms</t>
+          <t>665ms</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>413ms</t>
+          <t>488ms</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>736ms</t>
+          <t>616ms</t>
         </is>
       </c>
       <c r="L105" t="inlineStr"/>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>756ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>608ms</t>
+          <t>201ms</t>
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>414ms</t>
+          <t>824ms</t>
         </is>
       </c>
       <c r="L109" t="inlineStr"/>
@@ -7683,7 +7683,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>471ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
@@ -7749,7 +7749,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>271ms</t>
+          <t>287ms</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>247ms</t>
+          <t>171ms</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>694ms</t>
+          <t>292ms</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>472ms</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
@@ -8008,7 +8008,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>244ms</t>
+          <t>785ms</t>
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>334ms</t>
+          <t>415ms</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -8137,7 +8137,7 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>673ms</t>
+          <t>358ms</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -8202,7 +8202,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>149ms</t>
+          <t>548ms</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>195ms</t>
+          <t>306ms</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -8334,7 +8334,7 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>507ms</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>716ms</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>632ms</t>
+          <t>535ms</t>
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>720ms</t>
+          <t>227ms</t>
         </is>
       </c>
       <c r="L124" t="inlineStr"/>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>266ms</t>
+          <t>834ms</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>759ms</t>
+          <t>173ms</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -8795,7 +8795,7 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>120ms</t>
+          <t>371ms</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>675ms</t>
+          <t>360ms</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>539ms</t>
+          <t>751ms</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>742ms</t>
+          <t>451ms</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>394ms</t>
+          <t>541ms</t>
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
@@ -9124,7 +9124,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>200ms</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -9190,7 +9190,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>570ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>345ms</t>
+          <t>360ms</t>
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
@@ -9321,7 +9321,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>261ms</t>
+          <t>675ms</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>241ms</t>
+          <t>224ms</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
@@ -9453,7 +9453,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>551ms</t>
+          <t>314ms</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>129ms</t>
+          <t>148ms</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -9585,7 +9585,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>370ms</t>
+          <t>720ms</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -9651,7 +9651,7 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>291ms</t>
+          <t>826ms</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>539ms</t>
+          <t>709ms</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>142ms</t>
+          <t>212ms</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>774ms</t>
         </is>
       </c>
       <c r="L144" t="inlineStr"/>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>583ms</t>
+          <t>476ms</t>
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
@@ -10048,7 +10048,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>181ms</t>
+          <t>494ms</t>
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>612ms</t>
+          <t>627ms</t>
         </is>
       </c>
       <c r="L147" t="inlineStr"/>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>773ms</t>
+          <t>845ms</t>
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
@@ -10246,7 +10246,7 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>446ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
@@ -10312,7 +10312,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>651ms</t>
+          <t>154ms</t>
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
@@ -10377,7 +10377,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>603ms</t>
+          <t>794ms</t>
         </is>
       </c>
       <c r="L151" t="inlineStr"/>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>321ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L152" t="inlineStr"/>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>224ms</t>
+          <t>779ms</t>
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>601ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -10635,7 +10635,7 @@
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>183ms</t>
+          <t>189ms</t>
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>417ms</t>
+          <t>735ms</t>
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>316ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="L157" t="inlineStr"/>
@@ -10831,7 +10831,7 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>486ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
@@ -10963,7 +10963,7 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>364ms</t>
+          <t>455ms</t>
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
@@ -11029,7 +11029,7 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>437ms</t>
         </is>
       </c>
       <c r="L161" t="inlineStr"/>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>761ms</t>
+          <t>795ms</t>
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>170ms</t>
+          <t>220ms</t>
         </is>
       </c>
       <c r="L163" t="inlineStr"/>
@@ -11226,7 +11226,7 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>247ms</t>
+          <t>152ms</t>
         </is>
       </c>
       <c r="L164" t="inlineStr"/>
@@ -11292,7 +11292,7 @@
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>639ms</t>
+          <t>492ms</t>
         </is>
       </c>
       <c r="L165" t="inlineStr"/>
@@ -11358,7 +11358,7 @@
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t>148ms</t>
+          <t>634ms</t>
         </is>
       </c>
       <c r="L166" t="inlineStr"/>
@@ -11424,7 +11424,7 @@
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>529ms</t>
+          <t>222ms</t>
         </is>
       </c>
       <c r="L167" t="inlineStr"/>
@@ -11490,7 +11490,7 @@
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>573ms</t>
+          <t>593ms</t>
         </is>
       </c>
       <c r="L168" t="inlineStr"/>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>485ms</t>
+          <t>500ms</t>
         </is>
       </c>
       <c r="L169" t="inlineStr"/>
@@ -11621,7 +11621,7 @@
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>191ms</t>
+          <t>298ms</t>
         </is>
       </c>
       <c r="L170" t="inlineStr"/>
@@ -11687,7 +11687,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>469ms</t>
+          <t>528ms</t>
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
@@ -11753,7 +11753,7 @@
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>351ms</t>
+          <t>357ms</t>
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>453ms</t>
+          <t>485ms</t>
         </is>
       </c>
       <c r="L173" t="inlineStr"/>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>155ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="L174" t="inlineStr"/>
@@ -11950,7 +11950,7 @@
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>784ms</t>
         </is>
       </c>
       <c r="L175" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>672ms</t>
         </is>
       </c>
       <c r="L176" t="inlineStr"/>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t>823ms</t>
+          <t>549ms</t>
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
@@ -12148,7 +12148,7 @@
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>758ms</t>
         </is>
       </c>
       <c r="L178" t="inlineStr"/>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>193ms</t>
+          <t>739ms</t>
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
@@ -12279,7 +12279,7 @@
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>751ms</t>
+          <t>174ms</t>
         </is>
       </c>
       <c r="L180" t="inlineStr"/>
@@ -12345,7 +12345,7 @@
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>749ms</t>
+          <t>598ms</t>
         </is>
       </c>
       <c r="L181" t="inlineStr"/>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>242ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
@@ -12477,7 +12477,7 @@
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>215ms</t>
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>621ms</t>
+          <t>623ms</t>
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>376ms</t>
+          <t>605ms</t>
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
@@ -12677,7 +12677,7 @@
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>714ms</t>
+          <t>770ms</t>
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
@@ -12743,7 +12743,7 @@
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>671ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
@@ -12809,7 +12809,7 @@
       </c>
       <c r="K188" t="inlineStr">
         <is>
-          <t>440ms</t>
+          <t>258ms</t>
         </is>
       </c>
       <c r="L188" t="inlineStr"/>
@@ -12875,7 +12875,7 @@
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>630ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
@@ -12940,7 +12940,7 @@
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>225ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="L190" t="inlineStr"/>
@@ -13006,7 +13006,7 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>281ms</t>
+          <t>400ms</t>
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
@@ -13070,7 +13070,7 @@
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>488ms</t>
+          <t>177ms</t>
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
@@ -13134,7 +13134,7 @@
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>434ms</t>
+          <t>482ms</t>
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
@@ -13198,7 +13198,7 @@
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>379ms</t>
+          <t>590ms</t>
         </is>
       </c>
       <c r="L194" t="inlineStr"/>
@@ -13263,7 +13263,7 @@
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>296ms</t>
+          <t>604ms</t>
         </is>
       </c>
       <c r="L195" t="inlineStr"/>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>495ms</t>
+          <t>638ms</t>
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
@@ -13394,7 +13394,7 @@
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t>457ms</t>
+          <t>523ms</t>
         </is>
       </c>
       <c r="L197" t="inlineStr"/>
@@ -13460,7 +13460,7 @@
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>477ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>326ms</t>
+          <t>666ms</t>
         </is>
       </c>
       <c r="L199" t="inlineStr"/>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>456ms</t>
+          <t>121ms</t>
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>822ms</t>
+          <t>617ms</t>
         </is>
       </c>
       <c r="L201" t="inlineStr"/>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>512ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="L202" t="inlineStr"/>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>527ms</t>
+          <t>351ms</t>
         </is>
       </c>
       <c r="L203" t="inlineStr"/>
@@ -13855,7 +13855,7 @@
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>665ms</t>
         </is>
       </c>
       <c r="L204" t="inlineStr"/>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>159ms</t>
+          <t>796ms</t>
         </is>
       </c>
       <c r="L205" t="inlineStr"/>
@@ -13987,7 +13987,7 @@
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>280ms</t>
+          <t>703ms</t>
         </is>
       </c>
       <c r="L206" t="inlineStr"/>
@@ -14053,7 +14053,7 @@
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>774ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="L207" t="inlineStr"/>
@@ -14118,7 +14118,7 @@
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>209ms</t>
+          <t>168ms</t>
         </is>
       </c>
       <c r="L208" t="inlineStr"/>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>718ms</t>
+          <t>346ms</t>
         </is>
       </c>
       <c r="L209" t="inlineStr"/>
@@ -14250,7 +14250,7 @@
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>223ms</t>
+          <t>555ms</t>
         </is>
       </c>
       <c r="L210" t="inlineStr"/>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>480ms</t>
+          <t>211ms</t>
         </is>
       </c>
       <c r="L211" t="inlineStr"/>
@@ -14382,7 +14382,7 @@
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>554ms</t>
+          <t>663ms</t>
         </is>
       </c>
       <c r="L212" t="inlineStr"/>
@@ -14447,7 +14447,7 @@
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>479ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="L213" t="inlineStr"/>
@@ -14513,7 +14513,7 @@
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>312ms</t>
+          <t>341ms</t>
         </is>
       </c>
       <c r="L214" t="inlineStr"/>
@@ -14579,7 +14579,7 @@
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>468ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="L215" t="inlineStr"/>
@@ -14645,7 +14645,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>161ms</t>
+          <t>706ms</t>
         </is>
       </c>
       <c r="L216" t="inlineStr"/>
@@ -14711,7 +14711,7 @@
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>164ms</t>
+          <t>730ms</t>
         </is>
       </c>
       <c r="L217" t="inlineStr"/>
@@ -14777,7 +14777,7 @@
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>218ms</t>
+          <t>146ms</t>
         </is>
       </c>
       <c r="L218" t="inlineStr"/>
@@ -14842,7 +14842,7 @@
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>792ms</t>
+          <t>726ms</t>
         </is>
       </c>
       <c r="L219" t="inlineStr"/>
@@ -14908,7 +14908,7 @@
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>580ms</t>
+          <t>646ms</t>
         </is>
       </c>
       <c r="L220" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>646ms</t>
+          <t>822ms</t>
         </is>
       </c>
       <c r="L221" t="inlineStr"/>
@@ -15040,7 +15040,7 @@
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>277ms</t>
         </is>
       </c>
       <c r="L222" t="inlineStr"/>
@@ -15107,7 +15107,7 @@
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>650ms</t>
+          <t>225ms</t>
         </is>
       </c>
       <c r="L223" t="inlineStr"/>
@@ -15174,7 +15174,7 @@
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>584ms</t>
+          <t>180ms</t>
         </is>
       </c>
       <c r="L224" t="inlineStr"/>
@@ -15240,7 +15240,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>448ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="L225" t="inlineStr"/>
@@ -15306,7 +15306,7 @@
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t>769ms</t>
+          <t>361ms</t>
         </is>
       </c>
       <c r="L226" t="inlineStr"/>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t>731ms</t>
+          <t>783ms</t>
         </is>
       </c>
       <c r="L227" t="inlineStr"/>
@@ -15438,7 +15438,7 @@
       </c>
       <c r="K228" t="inlineStr">
         <is>
-          <t>515ms</t>
+          <t>579ms</t>
         </is>
       </c>
       <c r="L228" t="inlineStr"/>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="K229" t="inlineStr">
         <is>
-          <t>444ms</t>
+          <t>715ms</t>
         </is>
       </c>
       <c r="L229" t="inlineStr"/>
@@ -15569,7 +15569,7 @@
       </c>
       <c r="K230" t="inlineStr">
         <is>
-          <t>698ms</t>
+          <t>382ms</t>
         </is>
       </c>
       <c r="L230" t="inlineStr"/>
@@ -15633,7 +15633,7 @@
       </c>
       <c r="K231" t="inlineStr">
         <is>
-          <t>382ms</t>
+          <t>241ms</t>
         </is>
       </c>
       <c r="L231" t="inlineStr"/>
@@ -15697,7 +15697,7 @@
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>286ms</t>
+          <t>260ms</t>
         </is>
       </c>
       <c r="L232" t="inlineStr"/>
@@ -15761,7 +15761,7 @@
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>839ms</t>
+          <t>421ms</t>
         </is>
       </c>
       <c r="L233" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>547ms</t>
+          <t>837ms</t>
         </is>
       </c>
       <c r="L234" t="inlineStr"/>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="K235" t="inlineStr">
         <is>
-          <t>568ms</t>
+          <t>354ms</t>
         </is>
       </c>
       <c r="L235" t="inlineStr"/>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>733ms</t>
+          <t>772ms</t>
         </is>
       </c>
       <c r="L236" t="inlineStr"/>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t>627ms</t>
+          <t>430ms</t>
         </is>
       </c>
       <c r="L237" t="inlineStr"/>
@@ -16089,7 +16089,7 @@
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>137ms</t>
+          <t>356ms</t>
         </is>
       </c>
       <c r="L238" t="inlineStr"/>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>145ms</t>
         </is>
       </c>
       <c r="L239" t="inlineStr"/>
@@ -16221,7 +16221,7 @@
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>435ms</t>
+          <t>573ms</t>
         </is>
       </c>
       <c r="L240" t="inlineStr"/>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="K241" t="inlineStr">
         <is>
-          <t>366ms</t>
+          <t>714ms</t>
         </is>
       </c>
       <c r="L241" t="inlineStr"/>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>559ms</t>
+          <t>137ms</t>
         </is>
       </c>
       <c r="L242" t="inlineStr"/>
@@ -16418,7 +16418,7 @@
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>154ms</t>
+          <t>628ms</t>
         </is>
       </c>
       <c r="L243" t="inlineStr"/>
@@ -16484,7 +16484,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>725ms</t>
+          <t>144ms</t>
         </is>
       </c>
       <c r="L244" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K245" t="inlineStr">
         <is>
-          <t>402ms</t>
+          <t>834ms</t>
         </is>
       </c>
       <c r="L245" t="inlineStr"/>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>230ms</t>
+          <t>149ms</t>
         </is>
       </c>
       <c r="L246" t="inlineStr"/>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>632ms</t>
+          <t>244ms</t>
         </is>
       </c>
       <c r="L247" t="inlineStr"/>
@@ -16747,7 +16747,7 @@
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>493ms</t>
+          <t>195ms</t>
         </is>
       </c>
       <c r="L248" t="inlineStr"/>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="K249" t="inlineStr">
         <is>
-          <t>741ms</t>
+          <t>273ms</t>
         </is>
       </c>
       <c r="L249" t="inlineStr"/>
@@ -16879,7 +16879,7 @@
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>327ms</t>
+          <t>251ms</t>
         </is>
       </c>
       <c r="L250" t="inlineStr"/>
@@ -16945,7 +16945,7 @@
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>478ms</t>
+          <t>274ms</t>
         </is>
       </c>
       <c r="L251" t="inlineStr"/>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>292ms</t>
+          <t>502ms</t>
         </is>
       </c>
       <c r="L252" t="inlineStr"/>
@@ -17076,7 +17076,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>304ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="L253" t="inlineStr"/>
@@ -17142,7 +17142,7 @@
       </c>
       <c r="K254" t="inlineStr">
         <is>
-          <t>586ms</t>
+          <t>354ms</t>
         </is>
       </c>
       <c r="L254" t="inlineStr"/>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>813ms</t>
+          <t>471ms</t>
         </is>
       </c>
       <c r="L255" t="inlineStr"/>
@@ -17274,7 +17274,7 @@
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>399ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="L256" t="inlineStr"/>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>561ms</t>
         </is>
       </c>
       <c r="L257" t="inlineStr"/>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t>600ms</t>
+          <t>349ms</t>
         </is>
       </c>
       <c r="L258" t="inlineStr"/>
@@ -17471,7 +17471,7 @@
       </c>
       <c r="K259" t="inlineStr">
         <is>
-          <t>767ms</t>
+          <t>481ms</t>
         </is>
       </c>
       <c r="L259" t="inlineStr"/>
@@ -17537,7 +17537,7 @@
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>596ms</t>
+          <t>562ms</t>
         </is>
       </c>
       <c r="L260" t="inlineStr"/>
@@ -17603,7 +17603,7 @@
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>766ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="L261" t="inlineStr"/>
@@ -17670,7 +17670,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>568ms</t>
+          <t>481ms</t>
         </is>
       </c>
       <c r="L262" t="inlineStr"/>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>195ms</t>
+          <t>302ms</t>
         </is>
       </c>
       <c r="L263" t="inlineStr"/>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="K264" t="inlineStr">
         <is>
-          <t>707ms</t>
+          <t>808ms</t>
         </is>
       </c>
       <c r="L264" t="inlineStr"/>
@@ -17869,7 +17869,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>190ms</t>
+          <t>461ms</t>
         </is>
       </c>
       <c r="L265" t="inlineStr"/>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>667ms</t>
+          <t>833ms</t>
         </is>
       </c>
       <c r="L266" t="inlineStr"/>
@@ -18001,7 +18001,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>634ms</t>
+          <t>710ms</t>
         </is>
       </c>
       <c r="L267" t="inlineStr"/>
@@ -18066,7 +18066,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>428ms</t>
+          <t>187ms</t>
         </is>
       </c>
       <c r="L268" t="inlineStr"/>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t>768ms</t>
+          <t>492ms</t>
         </is>
       </c>
       <c r="L269" t="inlineStr"/>
@@ -18196,7 +18196,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>688ms</t>
+          <t>142ms</t>
         </is>
       </c>
       <c r="L270" t="inlineStr"/>
@@ -18260,7 +18260,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>484ms</t>
+          <t>525ms</t>
         </is>
       </c>
       <c r="L271" t="inlineStr"/>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>599ms</t>
+          <t>478ms</t>
         </is>
       </c>
       <c r="L272" t="inlineStr"/>
@@ -18389,7 +18389,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>317ms</t>
+          <t>242ms</t>
         </is>
       </c>
       <c r="L273" t="inlineStr"/>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>144ms</t>
+          <t>849ms</t>
         </is>
       </c>
       <c r="L274" t="inlineStr"/>
@@ -18520,7 +18520,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t>683ms</t>
+          <t>694ms</t>
         </is>
       </c>
       <c r="L275" t="inlineStr"/>
@@ -18586,7 +18586,7 @@
       </c>
       <c r="K276" t="inlineStr">
         <is>
-          <t>330ms</t>
+          <t>616ms</t>
         </is>
       </c>
       <c r="L276" t="inlineStr"/>
@@ -18652,7 +18652,7 @@
       </c>
       <c r="K277" t="inlineStr">
         <is>
-          <t>656ms</t>
+          <t>659ms</t>
         </is>
       </c>
       <c r="L277" t="inlineStr"/>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>644ms</t>
+          <t>228ms</t>
         </is>
       </c>
       <c r="L278" t="inlineStr"/>
@@ -18784,7 +18784,7 @@
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>567ms</t>
+          <t>413ms</t>
         </is>
       </c>
       <c r="L279" t="inlineStr"/>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>398ms</t>
+          <t>373ms</t>
         </is>
       </c>
       <c r="L280" t="inlineStr"/>
@@ -18915,7 +18915,7 @@
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>566ms</t>
+          <t>625ms</t>
         </is>
       </c>
       <c r="L281" t="inlineStr"/>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>201ms</t>
+          <t>380ms</t>
         </is>
       </c>
       <c r="L282" t="inlineStr"/>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>803ms</t>
+          <t>367ms</t>
         </is>
       </c>
       <c r="L283" t="inlineStr"/>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>420ms</t>
+          <t>424ms</t>
         </is>
       </c>
       <c r="L284" t="inlineStr"/>
@@ -19179,7 +19179,7 @@
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>623ms</t>
+          <t>332ms</t>
         </is>
       </c>
       <c r="L285" t="inlineStr"/>
@@ -19244,7 +19244,7 @@
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>613ms</t>
+          <t>299ms</t>
         </is>
       </c>
       <c r="L286" t="inlineStr"/>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>255ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="L287" t="inlineStr"/>
@@ -19376,7 +19376,7 @@
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>636ms</t>
+          <t>459ms</t>
         </is>
       </c>
       <c r="L288" t="inlineStr"/>
@@ -19442,7 +19442,7 @@
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>168ms</t>
+          <t>262ms</t>
         </is>
       </c>
       <c r="L289" t="inlineStr"/>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>461ms</t>
+          <t>688ms</t>
         </is>
       </c>
       <c r="L290" t="inlineStr"/>
@@ -19573,7 +19573,7 @@
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>404ms</t>
+          <t>436ms</t>
         </is>
       </c>
       <c r="L291" t="inlineStr"/>
@@ -19639,7 +19639,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>207ms</t>
+          <t>306ms</t>
         </is>
       </c>
       <c r="L292" t="inlineStr"/>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>510ms</t>
+          <t>282ms</t>
         </is>
       </c>
       <c r="L293" t="inlineStr"/>
@@ -19771,7 +19771,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>185ms</t>
+          <t>385ms</t>
         </is>
       </c>
       <c r="L294" t="inlineStr"/>
@@ -19837,7 +19837,7 @@
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>512ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L295" t="inlineStr"/>
@@ -19903,7 +19903,7 @@
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>167ms</t>
+          <t>564ms</t>
         </is>
       </c>
       <c r="L296" t="inlineStr"/>
@@ -19968,7 +19968,7 @@
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>465ms</t>
+          <t>264ms</t>
         </is>
       </c>
       <c r="L297" t="inlineStr"/>
@@ -20034,7 +20034,7 @@
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>323ms</t>
+          <t>632ms</t>
         </is>
       </c>
       <c r="L298" t="inlineStr"/>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>544ms</t>
+          <t>402ms</t>
         </is>
       </c>
       <c r="L299" t="inlineStr"/>
@@ -20166,7 +20166,7 @@
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>841ms</t>
+          <t>825ms</t>
         </is>
       </c>
       <c r="L300" t="inlineStr"/>
@@ -20233,7 +20233,7 @@
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>174ms</t>
+          <t>543ms</t>
         </is>
       </c>
       <c r="L301" t="inlineStr"/>
